--- a/data/export/2026-09-16-operations.xlsx
+++ b/data/export/2026-09-16-operations.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4809,7 +4809,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -7980,7 +7980,7 @@
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -8029,7 +8029,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8778,7 +8778,7 @@
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9393,7 +9393,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD72" s="2" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10886,7 +10886,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -11080,7 +11080,7 @@
       </c>
       <c r="P86" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q86" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD86" s="2" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11501,7 +11501,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD89" s="2" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11749,12 +11749,12 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11998,7 +11998,7 @@
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12160,27 +12160,31 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>21:18</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>69分钟</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:51采样，终点ETA 27分钟</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12188,7 +12192,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12212,12 +12216,12 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -12237,7 +12241,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>77.9</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
@@ -12280,7 +12284,7 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -12290,19 +12294,19 @@
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>20:51采样：该车到重点站东陆路新金桥路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数42分钟，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -12312,7 +12316,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12336,12 +12340,12 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -12361,7 +12365,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12409,26 +12413,22 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>22:04</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数74分钟估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 44分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12460,12 +12460,12 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12485,12 +12485,12 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -12533,7 +12533,7 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>22:27</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数72分钟估算，约±6分钟</t>
+          <t>21:21采样：该车到重点站长岛路台儿庄路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O98" s="2" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12589,7 +12589,7 @@
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="P99" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q99" s="2" t="inlineStr">
@@ -12733,12 +12733,12 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -12862,7 +12862,7 @@
       </c>
       <c r="AD100" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -12986,7 +12986,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -13110,7 +13110,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -13304,7 +13304,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13353,12 +13353,12 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -13482,7 +13482,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -13792,7 +13792,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="P109" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q109" s="2" t="inlineStr">
@@ -13961,7 +13961,7 @@
       </c>
       <c r="AC109" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AD109" s="2" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14152,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14196,17 +14196,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -14776,7 +14776,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14825,12 +14825,12 @@
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -14900,7 +14900,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14949,12 +14949,12 @@
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15073,7 +15073,7 @@
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
@@ -15392,7 +15392,7 @@
       </c>
       <c r="P121" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q121" s="2" t="inlineStr">
@@ -15570,7 +15570,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -15814,7 +15814,7 @@
       </c>
       <c r="AD124" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15884,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -16062,7 +16062,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -16132,7 +16132,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16181,12 +16181,12 @@
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -16636,7 +16636,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16685,12 +16685,12 @@
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -16814,7 +16814,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17177,7 +17177,7 @@
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
@@ -17252,7 +17252,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
@@ -17430,7 +17430,7 @@
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -17500,7 +17500,7 @@
       </c>
       <c r="P138" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q138" s="2" t="inlineStr">
@@ -17544,17 +17544,17 @@
       </c>
       <c r="AB138" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC138" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17624,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17673,12 +17673,12 @@
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -17872,7 +17872,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17921,12 +17921,12 @@
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -18050,7 +18050,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -18120,7 +18120,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18169,12 +18169,12 @@
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -18244,7 +18244,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18293,7 +18293,7 @@
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
@@ -18492,7 +18492,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="AD147" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -18740,7 +18740,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -19042,7 +19042,7 @@
       </c>
       <c r="AD150" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -19546,7 +19546,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -19918,7 +19918,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -20042,7 +20042,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -20236,7 +20236,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20285,7 +20285,7 @@
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
@@ -20414,7 +20414,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>7/30</t>
         </is>
       </c>
     </row>
@@ -20662,7 +20662,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -20786,7 +20786,7 @@
       </c>
       <c r="AD164" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AD166" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -21360,7 +21360,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21409,7 +21409,7 @@
       </c>
       <c r="AC169" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AD169" s="2" t="inlineStr">
@@ -21608,7 +21608,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21652,17 +21652,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -21980,7 +21980,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22029,12 +22029,12 @@
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -22104,7 +22104,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22153,12 +22153,12 @@
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -22228,7 +22228,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22352,7 +22352,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22401,12 +22401,12 @@
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -22476,7 +22476,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22650,7 +22650,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -22720,7 +22720,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22769,7 +22769,7 @@
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
@@ -23088,7 +23088,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23137,12 +23137,12 @@
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -23266,7 +23266,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -23390,7 +23390,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="AD188" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -23878,7 +23878,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -23944,7 +23944,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23993,12 +23993,12 @@
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -24404,27 +24404,31 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:41采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -24432,7 +24436,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24456,12 +24460,12 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
@@ -24481,7 +24485,7 @@
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>146.8</t>
+          <t>146.2</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
@@ -24524,7 +24528,7 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq44，推进16站，达到≥2站确认条件</t>
+          <t>原方向在全程51%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
@@ -24552,7 +24556,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24660,27 +24664,31 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="J196" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
       <c r="M196" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：20:50采样，终点ETA 32分钟</t>
-        </is>
-      </c>
-      <c r="N196" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N196" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24688,7 +24696,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24712,12 +24720,12 @@
       </c>
       <c r="X196" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y196" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z196" s="2" t="inlineStr">
@@ -24737,12 +24745,12 @@
       </c>
       <c r="AC196" s="2" t="inlineStr">
         <is>
-          <t>135.2</t>
+          <t>134.2</t>
         </is>
       </c>
       <c r="AD196" s="2" t="inlineStr">
         <is>
-          <t>7/30</t>
+          <t>6/30</t>
         </is>
       </c>
     </row>
@@ -24780,27 +24788,31 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="J197" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
       <c r="M197" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N197" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N197" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -24808,7 +24820,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24832,17 +24844,17 @@
       </c>
       <c r="X197" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y197" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z197" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA197" s="2" t="inlineStr">
@@ -24852,17 +24864,17 @@
       </c>
       <c r="AB197" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC197" s="2" t="inlineStr">
         <is>
-          <t>145.3</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -25020,7 +25032,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq30，推进2站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq48，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -25048,7 +25060,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25161,26 +25173,22 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>21:32</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>113分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>20:50采样：该车到重点站云山路碧云路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数38分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N200" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 22分钟</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr"/>
       <c r="O200" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -25188,7 +25196,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25212,12 +25220,12 @@
       </c>
       <c r="X200" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y200" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z200" s="2" t="inlineStr">
@@ -25237,12 +25245,12 @@
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>136.5</t>
+          <t>139.0</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -25285,26 +25293,22 @@
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>21:46</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>20:50采样：该车到重点站沪南路北中路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数49分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N201" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 25分钟</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr"/>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -25312,7 +25316,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25336,12 +25340,12 @@
       </c>
       <c r="X201" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
@@ -25361,12 +25365,12 @@
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>142.8</t>
+          <t>142.5</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -25409,24 +25413,24 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>22:09</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr"/>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>20:50采样：该车到重点站丁香路锦绣路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数71分钟，约±9分钟</t>
+          <t>21:20采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N202" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O202" s="2" t="inlineStr">
@@ -25436,7 +25440,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25485,7 +25489,7 @@
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
@@ -25533,19 +25537,19 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>22:13</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr"/>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>20:50采样：该车到重点站沪南路高科西路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数78分钟，约±5分钟</t>
+          <t>21:20采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N203" s="2" t="inlineStr">
@@ -25560,7 +25564,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25609,7 +25613,7 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>139.5</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
@@ -25657,24 +25661,24 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>22:42</t>
+          <t>22:40</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr"/>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>20:50采样：该车到重点站川周公路康沈路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数109分钟，约±6分钟</t>
+          <t>21:20采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±7分钟</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O204" s="2" t="inlineStr">
@@ -25684,7 +25688,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25733,12 +25737,12 @@
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>141.5</t>
+          <t>141.2</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -25781,24 +25785,24 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>23:01</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr"/>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数126分钟估算，约±5分钟</t>
+          <t>21:20采样：该车到重点站沪南路华夏西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O205" s="2" t="inlineStr">
@@ -25808,7 +25812,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25837,7 +25841,7 @@
       </c>
       <c r="Y205" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z205" s="2" t="inlineStr">
@@ -25857,12 +25861,12 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>6/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -25928,7 +25932,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25977,12 +25981,12 @@
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -26350,7 +26354,7 @@
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -26416,7 +26420,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26460,17 +26464,17 @@
       </c>
       <c r="AB210" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -26540,7 +26544,7 @@
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q211" s="2" t="inlineStr">
@@ -26589,7 +26593,7 @@
       </c>
       <c r="AC211" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AD211" s="2" t="inlineStr">
@@ -26718,7 +26722,7 @@
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -26912,7 +26916,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26961,7 +26965,7 @@
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
@@ -27334,7 +27338,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -27652,7 +27656,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27701,12 +27705,12 @@
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -27772,7 +27776,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27821,12 +27825,12 @@
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -28442,7 +28446,7 @@
       </c>
       <c r="AD226" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -28512,7 +28516,7 @@
       </c>
       <c r="P227" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q227" s="2" t="inlineStr">
@@ -28561,7 +28565,7 @@
       </c>
       <c r="AC227" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AD227" s="2" t="inlineStr">
@@ -28632,7 +28636,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28676,17 +28680,17 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -28810,7 +28814,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -29000,7 +29004,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29049,7 +29053,7 @@
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
@@ -29422,7 +29426,7 @@
       </c>
       <c r="AD234" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -29616,7 +29620,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29665,12 +29669,12 @@
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -30042,7 +30046,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -30108,7 +30112,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30169,7 +30173,7 @@
       </c>
       <c r="AC240" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AD240" s="2" t="inlineStr">
@@ -30422,7 +30426,7 @@
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -30918,7 +30922,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -31290,7 +31294,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31538,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -32030,7 +32034,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -32402,7 +32406,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -32596,7 +32600,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32645,12 +32649,12 @@
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -32774,7 +32778,7 @@
       </c>
       <c r="AD261" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -33216,7 +33220,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33260,17 +33264,17 @@
       </c>
       <c r="AB265" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -33588,7 +33592,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33637,7 +33641,7 @@
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
@@ -33712,7 +33716,7 @@
       </c>
       <c r="P269" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q269" s="2" t="inlineStr">
@@ -33761,7 +33765,7 @@
       </c>
       <c r="AC269" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AD269" s="2" t="inlineStr">
@@ -33890,7 +33894,7 @@
       </c>
       <c r="AD270" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -34084,7 +34088,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34133,12 +34137,12 @@
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -34262,7 +34266,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -34456,7 +34460,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34505,12 +34509,12 @@
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -34758,7 +34762,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>15/17</t>
         </is>
       </c>
     </row>
@@ -35200,7 +35204,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35244,17 +35248,17 @@
       </c>
       <c r="AB281" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -35448,7 +35452,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35497,7 +35501,7 @@
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
@@ -35750,7 +35754,7 @@
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>12/17</t>
         </is>
       </c>
     </row>
@@ -35820,7 +35824,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -35869,12 +35873,12 @@
       </c>
       <c r="AC286" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -36188,7 +36192,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36237,7 +36241,7 @@
       </c>
       <c r="AC289" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AD289" s="2" t="inlineStr">
@@ -36486,7 +36490,7 @@
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>16/17</t>
+          <t>17/17</t>
         </is>
       </c>
     </row>
@@ -36552,7 +36556,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q292" s="2" t="inlineStr">
@@ -36601,12 +36605,12 @@
       </c>
       <c r="AC292" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -37044,7 +37048,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37088,17 +37092,17 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -37292,7 +37296,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37341,7 +37345,7 @@
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
@@ -37389,12 +37393,12 @@
       </c>
       <c r="I299" s="2" t="inlineStr">
         <is>
-          <t>21:14</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="J299" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K299" s="2" t="inlineStr"/>
@@ -37416,7 +37420,7 @@
       </c>
       <c r="P299" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="Q299" s="2" t="inlineStr">
@@ -37465,7 +37469,7 @@
       </c>
       <c r="AC299" s="2" t="inlineStr">
         <is>
-          <t>90.6</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AD299" s="2" t="inlineStr">
@@ -37513,24 +37517,24 @@
       </c>
       <c r="I300" s="2" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>21:24</t>
         </is>
       </c>
       <c r="J300" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr"/>
       <c r="M300" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N300" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O300" s="2" t="inlineStr">
@@ -37540,7 +37544,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37589,12 +37593,12 @@
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>
@@ -37632,29 +37636,29 @@
       </c>
       <c r="H301" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>21:38</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
       <c r="L301" s="2" t="inlineStr"/>
       <c r="M301" s="2" t="inlineStr">
         <is>
-          <t>20:50采样：该车到重点站金高路源华路 ETA 6分钟；叠加该车自身同类时段从该站到终点历史中位数53分钟，约±11分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N301" s="2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O301" s="2" t="inlineStr">
@@ -37664,7 +37668,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37688,12 +37692,12 @@
       </c>
       <c r="X301" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y301" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z301" s="2" t="inlineStr">
@@ -37713,12 +37717,12 @@
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>94.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>14/17</t>
+          <t>13/17</t>
         </is>
       </c>
     </row>
@@ -37756,27 +37760,31 @@
       </c>
       <c r="H302" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N302" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N302" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O302" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -37784,7 +37792,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37808,17 +37816,17 @@
       </c>
       <c r="X302" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y302" s="2" t="inlineStr">
         <is>
-          <t>证据不足</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z302" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA302" s="2" t="inlineStr">
@@ -37828,17 +37836,17 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>97.8</t>
+          <t>95.7</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>17/17</t>
+          <t>16/17</t>
         </is>
       </c>
     </row>
@@ -37881,24 +37889,24 @@
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:36</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数90分钟估算，约±13分钟</t>
+          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±10分钟</t>
         </is>
       </c>
       <c r="N303" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="O303" s="2" t="inlineStr">
@@ -37908,7 +37916,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37932,12 +37940,12 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
@@ -37957,7 +37965,7 @@
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
@@ -38032,7 +38040,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38081,12 +38089,12 @@
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>10/17</t>
+          <t>11/17</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-16-operations.xlsx
+++ b/data/export/2026-09-16-operations.xlsx
@@ -447,7 +447,7 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
     <col width="36" customWidth="1" min="21" max="21"/>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1721,12 +1721,12 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5057,12 +5057,12 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6173,12 +6173,12 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6421,12 +6421,12 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8649,12 +8649,12 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -9592,7 +9592,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -11452,7 +11452,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11749,12 +11749,12 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12117,12 +12117,12 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12408,27 +12408,31 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:03</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:21采样，终点ETA 44分钟</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -12436,7 +12440,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12460,12 +12464,12 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12485,12 +12489,12 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>11/15</t>
+          <t>10/15</t>
         </is>
       </c>
     </row>
@@ -12533,19 +12537,19 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>22:26</t>
+          <t>22:28</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>72分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>21:21采样：该车到重点站长岛路台儿庄路 ETA 5分钟；叠加该车自身同类时段从该站到终点历史中位数60分钟，约±5分钟</t>
+          <t>21:31采样：该车到重点站东陆路新金桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N98" s="2" t="inlineStr">
@@ -12560,7 +12564,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12609,12 +12613,12 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>79.9</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>10/15</t>
+          <t>11/15</t>
         </is>
       </c>
     </row>
@@ -13186,14 +13190,18 @@
       </c>
       <c r="R103" s="2" t="inlineStr">
         <is>
-          <t>迎春路长柳路</t>
-        </is>
-      </c>
-      <c r="S103" s="2" t="inlineStr"/>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S103" s="2" t="inlineStr">
+        <is>
+          <t>07:43</t>
+        </is>
+      </c>
       <c r="T103" s="2" t="inlineStr"/>
       <c r="U103" s="2" t="inlineStr">
         <is>
-          <t>区间折返已由主分类器确认；现有采样不足以把折返发车时间控制在±10分钟</t>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq24映射；现有采样不足以把折返发车时间控制在±10分钟</t>
         </is>
       </c>
       <c r="V103" s="2" t="inlineStr">
@@ -13304,7 +13312,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13353,7 +13361,7 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
@@ -13726,7 +13734,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -13792,7 +13800,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13841,12 +13849,12 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -14206,7 +14214,7 @@
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -14282,7 +14290,7 @@
       </c>
       <c r="R112" s="2" t="inlineStr">
         <is>
-          <t>沪南路高科西路</t>
+          <t>物理seq23（站名待映射）</t>
         </is>
       </c>
       <c r="S112" s="2" t="inlineStr">
@@ -14297,7 +14305,7 @@
       </c>
       <c r="U112" s="2" t="inlineStr">
         <is>
-          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±7分钟；反向重点站沪南路北中路 ETA 4分钟参与校验</t>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 4分钟参与校验</t>
         </is>
       </c>
       <c r="V112" s="2" t="inlineStr">
@@ -14342,7 +14350,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -14408,7 +14416,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14457,12 +14465,12 @@
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -14776,7 +14784,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14900,7 +14908,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14949,7 +14957,7 @@
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
@@ -15024,7 +15032,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15073,12 +15081,12 @@
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -15202,7 +15210,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -15884,7 +15892,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -16510,7 +16518,7 @@
       </c>
       <c r="R130" s="2" t="inlineStr">
         <is>
-          <t>迎春路长柳路</t>
+          <t>物理seq32（站名待映射）</t>
         </is>
       </c>
       <c r="S130" s="2" t="inlineStr">
@@ -16525,7 +16533,7 @@
       </c>
       <c r="U130" s="2" t="inlineStr">
         <is>
-          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±5分钟；反向重点站锦绣路花木路 ETA 0分钟参与校验</t>
+          <t>折返点按重建物理位置seq32映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
         </is>
       </c>
       <c r="V130" s="2" t="inlineStr">
@@ -16636,7 +16644,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16685,7 +16693,7 @@
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
@@ -17058,7 +17066,7 @@
       </c>
       <c r="AD134" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17136,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17177,12 +17185,12 @@
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -17554,7 +17562,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -17624,7 +17632,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17673,12 +17681,12 @@
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -17872,7 +17880,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -18120,7 +18128,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18169,7 +18177,7 @@
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
@@ -18244,7 +18252,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18293,12 +18301,12 @@
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -18422,7 +18430,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -18740,7 +18748,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -19290,7 +19298,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -19366,7 +19374,7 @@
       </c>
       <c r="R153" s="2" t="inlineStr">
         <is>
-          <t>沪南路高科西路</t>
+          <t>物理seq24（站名待映射）</t>
         </is>
       </c>
       <c r="S153" s="2" t="inlineStr">
@@ -19381,7 +19389,7 @@
       </c>
       <c r="U153" s="2" t="inlineStr">
         <is>
-          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±9分钟；反向重点站沪南路北中路 ETA 9分钟参与校验</t>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 9分钟参与校验</t>
         </is>
       </c>
       <c r="V153" s="2" t="inlineStr">
@@ -19794,7 +19802,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -20166,7 +20174,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -20236,7 +20244,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20285,12 +20293,12 @@
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -21234,22 +21242,22 @@
       </c>
       <c r="R168" s="2" t="inlineStr">
         <is>
-          <t>迎春路长柳路</t>
+          <t>物理seq28（站名待映射）</t>
         </is>
       </c>
       <c r="S168" s="2" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="T168" s="2" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="U168" s="2" t="inlineStr">
         <is>
-          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±7分钟；反向重点站锦绣路花木路 ETA 0分钟参与校验</t>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
         </is>
       </c>
       <c r="V168" s="2" t="inlineStr">
@@ -21662,7 +21670,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -21910,7 +21918,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -21980,7 +21988,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22352,7 +22360,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22401,7 +22409,7 @@
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
@@ -22476,7 +22484,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22720,7 +22728,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22769,12 +22777,12 @@
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -23022,7 +23030,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -23088,7 +23096,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23137,12 +23145,12 @@
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -23634,7 +23642,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -23944,7 +23952,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -23993,7 +24001,7 @@
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
@@ -24581,7 +24589,7 @@
       </c>
       <c r="U195" s="2" t="inlineStr">
         <is>
-          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±5分钟；反向重点站锦绣路花木路 ETA 0分钟参与校验</t>
+          <t>折返点按重建物理位置seq33映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
         </is>
       </c>
       <c r="V195" s="2" t="inlineStr">
@@ -24874,7 +24882,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -24994,7 +25002,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -25032,7 +25040,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq48，推进20站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -25060,7 +25068,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25070,22 +25078,22 @@
       </c>
       <c r="R199" s="2" t="inlineStr">
         <is>
-          <t>迎春路长柳路</t>
+          <t>物理seq27（站名待映射）</t>
         </is>
       </c>
       <c r="S199" s="2" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="T199" s="2" t="inlineStr">
         <is>
-          <t>20:34</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="U199" s="2" t="inlineStr">
         <is>
-          <t>到达按末次同向重点站ETA估算；折返发车结合首次反向运行观测取区间中点，约±6分钟；反向重点站锦绣路花木路 ETA 0分钟参与校验</t>
+          <t>折返点按重建物理位置seq27映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
         </is>
       </c>
       <c r="V199" s="2" t="inlineStr">
@@ -25168,27 +25176,31 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>21:42</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>123分钟</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 22分钟</t>
-        </is>
-      </c>
-      <c r="N200" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -25196,7 +25208,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25220,12 +25232,12 @@
       </c>
       <c r="X200" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y200" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z200" s="2" t="inlineStr">
@@ -25245,7 +25257,7 @@
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>139.0</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
@@ -25288,12 +25300,12 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
@@ -25305,10 +25317,14 @@
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:20采样，终点ETA 25分钟</t>
-        </is>
-      </c>
-      <c r="N201" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>07:10</t>
@@ -25316,7 +25332,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25340,12 +25356,12 @@
       </c>
       <c r="X201" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
@@ -25413,26 +25429,22 @@
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>22:09</t>
+          <t>22:12</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr"/>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路北中路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数48分钟，约±10分钟</t>
-        </is>
-      </c>
-      <c r="N202" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:31采样，终点ETA 41分钟</t>
+        </is>
+      </c>
+      <c r="N202" s="2" t="inlineStr"/>
       <c r="O202" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -25440,7 +25452,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25464,12 +25476,12 @@
       </c>
       <c r="X202" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y202" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z202" s="2" t="inlineStr">
@@ -25489,12 +25501,12 @@
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -25542,14 +25554,14 @@
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr"/>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站云山路碧云路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数50分钟，约±5分钟</t>
+          <t>21:31采样：该车到重点站长岛路张杨北路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N203" s="2" t="inlineStr">
@@ -25564,7 +25576,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25613,12 +25625,12 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>139.8</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -25661,24 +25673,24 @@
       </c>
       <c r="I204" s="2" t="inlineStr">
         <is>
-          <t>22:40</t>
+          <t>22:39</t>
         </is>
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr"/>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路高科西路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数80分钟，约±7分钟</t>
+          <t>21:31采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O204" s="2" t="inlineStr">
@@ -25688,7 +25700,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25737,12 +25749,12 @@
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>140.8</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -25785,19 +25797,19 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>22:51</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>116分钟</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr"/>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站沪南路华夏西路 ETA 9分钟；叠加该车自身同类时段从该站到终点历史中位数86分钟，约±6分钟</t>
+          <t>21:31采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±6分钟</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
@@ -25812,7 +25824,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25861,7 +25873,7 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.7</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
@@ -25932,7 +25944,7 @@
       </c>
       <c r="P206" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q206" s="2" t="inlineStr">
@@ -25981,12 +25993,12 @@
       </c>
       <c r="AC206" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -26420,7 +26432,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26469,7 +26481,7 @@
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
@@ -26916,7 +26928,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -27656,7 +27668,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27776,7 +27788,7 @@
       </c>
       <c r="P221" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q221" s="2" t="inlineStr">
@@ -27825,12 +27837,12 @@
       </c>
       <c r="AC221" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -28636,7 +28648,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28685,7 +28697,7 @@
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
@@ -29004,7 +29016,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29620,7 +29632,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -30122,7 +30134,7 @@
       </c>
       <c r="R240" s="2" t="inlineStr">
         <is>
-          <t>五莲路东陆路</t>
+          <t>五莲路荷泽路</t>
         </is>
       </c>
       <c r="S240" s="2" t="inlineStr">
@@ -30133,7 +30145,7 @@
       <c r="T240" s="2" t="inlineStr"/>
       <c r="U240" s="2" t="inlineStr">
         <is>
-          <t>区间折返已由主分类器确认；现有采样不足以把折返发车时间控制在±10分钟</t>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq16映射；现有采样不足以把折返发车时间控制在±10分钟</t>
         </is>
       </c>
       <c r="V240" s="2" t="inlineStr">
@@ -32600,7 +32612,7 @@
       </c>
       <c r="P260" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q260" s="2" t="inlineStr">
@@ -32649,12 +32661,12 @@
       </c>
       <c r="AC260" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -33220,7 +33232,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33269,7 +33281,7 @@
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
@@ -33592,7 +33604,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -34088,7 +34100,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34460,7 +34472,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34509,12 +34521,12 @@
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -35204,7 +35216,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35253,7 +35265,7 @@
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
@@ -35452,7 +35464,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35824,7 +35836,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -36556,7 +36568,7 @@
       </c>
       <c r="P292" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q292" s="2" t="inlineStr">
@@ -36605,12 +36617,12 @@
       </c>
       <c r="AC292" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -37048,7 +37060,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37097,7 +37109,7 @@
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
@@ -37296,7 +37308,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37544,7 +37556,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37641,12 +37653,12 @@
       </c>
       <c r="I301" s="2" t="inlineStr">
         <is>
-          <t>21:38</t>
+          <t>21:39</t>
         </is>
       </c>
       <c r="J301" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K301" s="2" t="inlineStr"/>
@@ -37668,7 +37680,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37717,12 +37729,12 @@
       </c>
       <c r="AC301" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>93.2</t>
         </is>
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>13/17</t>
+          <t>14/17</t>
         </is>
       </c>
     </row>
@@ -37765,24 +37777,24 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>22:04</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O302" s="2" t="inlineStr">
@@ -37792,7 +37804,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37841,7 +37853,7 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>95.7</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
@@ -37916,7 +37928,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -38040,7 +38052,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">

--- a/data/export/2026-09-16-operations.xlsx
+++ b/data/export/2026-09-16-operations.xlsx
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8848,7 +8848,7 @@
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8897,7 +8897,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD68" s="2" t="inlineStr">
@@ -9592,7 +9592,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -10088,7 +10088,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -11452,7 +11452,7 @@
       </c>
       <c r="P89" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q89" s="2" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -12068,7 +12068,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12301,12 +12301,12 @@
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12440,7 +12440,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12537,26 +12537,22 @@
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>22:28</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>21:31采样：该车到重点站东陆路新金桥路 ETA 14分钟；叠加该车自身同类时段从该站到终点历史中位数43分钟，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N98" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>SHMAAS末次终点ETA推算：21:51采样，终点ETA 38分钟</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
       <c r="O98" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -12564,7 +12560,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12588,12 +12584,12 @@
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>末次终点ETA兜底</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12613,7 +12609,7 @@
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
@@ -13114,7 +13110,7 @@
       </c>
       <c r="AD102" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -13312,7 +13308,7 @@
       </c>
       <c r="P104" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q104" s="2" t="inlineStr">
@@ -13361,12 +13357,12 @@
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -13800,7 +13796,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13849,12 +13845,12 @@
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -14350,7 +14346,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -14416,7 +14412,7 @@
       </c>
       <c r="P113" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q113" s="2" t="inlineStr">
@@ -14465,7 +14461,7 @@
       </c>
       <c r="AC113" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD113" s="2" t="inlineStr">
@@ -14714,7 +14710,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -14784,7 +14780,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14908,7 +14904,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -14957,12 +14953,12 @@
       </c>
       <c r="AC117" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD117" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -15032,7 +15028,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15081,7 +15077,7 @@
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
@@ -15210,7 +15206,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -15892,7 +15888,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -16442,7 +16438,7 @@
       </c>
       <c r="AD129" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -16644,7 +16640,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16693,12 +16689,12 @@
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -17136,7 +17132,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17185,12 +17181,12 @@
       </c>
       <c r="AC135" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -17632,7 +17628,7 @@
       </c>
       <c r="P139" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q139" s="2" t="inlineStr">
@@ -17681,7 +17677,7 @@
       </c>
       <c r="AC139" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD139" s="2" t="inlineStr">
@@ -17880,7 +17876,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -18058,7 +18054,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -18128,7 +18124,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18177,12 +18173,12 @@
       </c>
       <c r="AC143" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD143" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -18252,7 +18248,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18301,7 +18297,7 @@
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
@@ -18430,7 +18426,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -18748,7 +18744,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -18926,7 +18922,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19550,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -19802,7 +19798,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -19926,7 +19922,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -20174,7 +20170,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -20244,7 +20240,7 @@
       </c>
       <c r="P160" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q160" s="2" t="inlineStr">
@@ -20293,7 +20289,7 @@
       </c>
       <c r="AC160" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AD160" s="2" t="inlineStr">
@@ -20670,7 +20666,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -21166,7 +21162,7 @@
       </c>
       <c r="AD167" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -21918,7 +21914,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -21988,7 +21984,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22360,7 +22356,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22409,12 +22405,12 @@
       </c>
       <c r="AC177" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD177" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -22484,7 +22480,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22728,7 +22724,7 @@
       </c>
       <c r="P180" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q180" s="2" t="inlineStr">
@@ -22777,12 +22773,12 @@
       </c>
       <c r="AC180" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD180" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -23096,7 +23092,7 @@
       </c>
       <c r="P183" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q183" s="2" t="inlineStr">
@@ -23145,7 +23141,7 @@
       </c>
       <c r="AC183" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD183" s="2" t="inlineStr">
@@ -23398,7 +23394,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>3/30</t>
+          <t>2/30</t>
         </is>
       </c>
     </row>
@@ -23642,7 +23638,7 @@
       </c>
       <c r="AD187" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -23886,7 +23882,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -23952,7 +23948,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -24001,12 +23997,12 @@
       </c>
       <c r="AC190" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD190" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -25002,7 +24998,7 @@
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -25040,7 +25036,7 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq54，推进26站，达到≥2站确认条件</t>
+          <t>原方向在全程41%处后消失；随后反向物理轨迹由seq28推进至seq59，推进31站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
@@ -25068,7 +25064,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25181,24 +25177,24 @@
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>21:41</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>121分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N200" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O200" s="2" t="inlineStr">
@@ -25208,7 +25204,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25257,12 +25253,12 @@
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>138.5</t>
+          <t>139.5</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -25332,7 +25328,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25424,27 +25420,31 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I202" s="2" t="inlineStr">
         <is>
-          <t>22:12</t>
+          <t>22:11</t>
         </is>
       </c>
       <c r="J202" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr"/>
       <c r="M202" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS末次终点ETA推算：21:31采样，终点ETA 41分钟</t>
-        </is>
-      </c>
-      <c r="N202" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N202" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -25452,7 +25452,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25476,12 +25476,12 @@
       </c>
       <c r="X202" s="2" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y202" s="2" t="inlineStr">
         <is>
-          <t>末次终点ETA兜底</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z202" s="2" t="inlineStr">
@@ -25501,7 +25501,7 @@
       </c>
       <c r="AC202" s="2" t="inlineStr">
         <is>
-          <t>140.5</t>
+          <t>140.2</t>
         </is>
       </c>
       <c r="AD202" s="2" t="inlineStr">
@@ -25549,19 +25549,19 @@
       </c>
       <c r="I203" s="2" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="J203" s="2" t="inlineStr">
         <is>
-          <t>128分钟</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr"/>
       <c r="M203" s="2" t="inlineStr">
         <is>
-          <t>21:31采样：该车到重点站长岛路张杨北路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数35分钟，约±5分钟</t>
+          <t>21:50采样：该车到重点站东波路莱阳路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数16分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N203" s="2" t="inlineStr">
@@ -25576,7 +25576,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25625,12 +25625,12 @@
       </c>
       <c r="AC203" s="2" t="inlineStr">
         <is>
-          <t>139.8</t>
+          <t>138.8</t>
         </is>
       </c>
       <c r="AD203" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -25678,14 +25678,14 @@
       </c>
       <c r="J204" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr"/>
       <c r="M204" s="2" t="inlineStr">
         <is>
-          <t>21:31采样：该车到重点站锦绣路花木路 ETA 0分钟；叠加该车自身同类时段从该站到终点历史中位数68分钟，约±5分钟</t>
+          <t>21:50采样：该车到重点站云山路碧云路 ETA 2分钟；叠加该车自身同类时段从该站到终点历史中位数47分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N204" s="2" t="inlineStr">
@@ -25700,7 +25700,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25749,7 +25749,7 @@
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>140.8</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25797,24 +25797,24 @@
       </c>
       <c r="I205" s="2" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>22:57</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>116分钟</t>
+          <t>123分钟</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr"/>
       <c r="M205" s="2" t="inlineStr">
         <is>
-          <t>21:31采样：该车到重点站沪南路高科西路 ETA 8分钟；叠加该车自身同类时段从该站到终点历史中位数72分钟，约±6分钟</t>
+          <t>21:50采样：该车到重点站迎春路金松路 ETA 3分钟；叠加该车自身同类时段从该站到终点历史中位数64分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N205" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O205" s="2" t="inlineStr">
@@ -25824,7 +25824,7 @@
       </c>
       <c r="P205" s="2" t="inlineStr">
         <is>
-          <t>21:31</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q205" s="2" t="inlineStr">
@@ -25873,12 +25873,12 @@
       </c>
       <c r="AC205" s="2" t="inlineStr">
         <is>
-          <t>131.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>2/30</t>
+          <t>3/30</t>
         </is>
       </c>
     </row>
@@ -26432,7 +26432,7 @@
       </c>
       <c r="P210" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q210" s="2" t="inlineStr">
@@ -26481,7 +26481,7 @@
       </c>
       <c r="AC210" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD210" s="2" t="inlineStr">
@@ -26928,7 +26928,7 @@
       </c>
       <c r="P214" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q214" s="2" t="inlineStr">
@@ -26977,7 +26977,7 @@
       </c>
       <c r="AC214" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD214" s="2" t="inlineStr">
@@ -27668,7 +27668,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -28648,7 +28648,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28697,7 +28697,7 @@
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
@@ -29016,7 +29016,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29065,7 +29065,7 @@
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
@@ -29632,7 +29632,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -33232,7 +33232,7 @@
       </c>
       <c r="P265" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q265" s="2" t="inlineStr">
@@ -33281,7 +33281,7 @@
       </c>
       <c r="AC265" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD265" s="2" t="inlineStr">
@@ -33604,7 +33604,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33653,7 +33653,7 @@
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
@@ -34100,7 +34100,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -35216,7 +35216,7 @@
       </c>
       <c r="P281" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q281" s="2" t="inlineStr">
@@ -35265,7 +35265,7 @@
       </c>
       <c r="AC281" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD281" s="2" t="inlineStr">
@@ -35464,7 +35464,7 @@
       </c>
       <c r="P283" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q283" s="2" t="inlineStr">
@@ -35513,7 +35513,7 @@
       </c>
       <c r="AC283" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD283" s="2" t="inlineStr">
@@ -35836,7 +35836,7 @@
       </c>
       <c r="P286" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q286" s="2" t="inlineStr">
@@ -37060,7 +37060,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37109,7 +37109,7 @@
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
@@ -37308,7 +37308,7 @@
       </c>
       <c r="P298" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q298" s="2" t="inlineStr">
@@ -37357,7 +37357,7 @@
       </c>
       <c r="AC298" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD298" s="2" t="inlineStr">
@@ -37556,7 +37556,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37777,24 +37777,24 @@
       </c>
       <c r="I302" s="2" t="inlineStr">
         <is>
-          <t>22:04</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="J302" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="K302" s="2" t="inlineStr"/>
       <c r="L302" s="2" t="inlineStr"/>
       <c r="M302" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="N302" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O302" s="2" t="inlineStr">
@@ -37804,7 +37804,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37853,7 +37853,7 @@
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
@@ -37896,29 +37896,29 @@
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>22:36</t>
+          <t>22:29</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>21:20采样：该车到重点站金杨路枣庄路 ETA 7分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±10分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="N303" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O303" s="2" t="inlineStr">
@@ -37928,7 +37928,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37952,12 +37952,12 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>同车重点站剩余时间</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
@@ -37977,7 +37977,7 @@
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
@@ -38025,7 +38025,7 @@
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>23:03</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
@@ -38037,7 +38037,7 @@
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>按该车自身同方向、同类时段历史全程时间中位数84分钟估算，约±5分钟</t>
+          <t>21:50采样：该车到重点站金杨路云山路 ETA 4分钟；叠加该车自身同类时段从该站到终点历史中位数69分钟，约±5分钟</t>
         </is>
       </c>
       <c r="N304" s="2" t="inlineStr">
@@ -38052,7 +38052,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38081,7 +38081,7 @@
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>同车历史全程时间</t>
+          <t>同车重点站剩余时间</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
